--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:30:59+00:00</t>
+    <t>2026-06-25T13:36:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:36:44+00:00</t>
+    <t>2026-06-25T13:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:46:53+00:00</t>
+    <t>2026-06-25T14:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:00:23+00:00</t>
+    <t>2026-06-25T14:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:06:22+00:00</t>
+    <t>2026-06-25T14:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:22:09+00:00</t>
+    <t>2026-06-25T14:35:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
+++ b/test-workflow-container/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:35:30+00:00</t>
+    <t>2026-06-25T14:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
